--- a/military_final.xlsx
+++ b/military_final.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY146"/>
+  <dimension ref="A1:BA146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,6 +685,16 @@
           <t>coalition_asset_share</t>
         </is>
       </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>is_nato</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -842,6 +852,14 @@
       <c r="AY2" t="n">
         <v>0.1411031003285632</v>
       </c>
+      <c r="AZ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -999,6 +1017,14 @@
       <c r="AY3" t="n">
         <v>0.08144785811052804</v>
       </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1156,6 +1182,14 @@
       <c r="AY4" t="n">
         <v>0.08457777293324406</v>
       </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1313,6 +1347,14 @@
       <c r="AY5" t="n">
         <v>0.05234432177392984</v>
       </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1470,6 +1512,14 @@
       <c r="AY6" t="n">
         <v>0.03157165324903845</v>
       </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1627,6 +1677,14 @@
       <c r="AY7" t="n">
         <v>0.007528924461607935</v>
       </c>
+      <c r="AZ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1784,6 +1842,14 @@
       <c r="AY8" t="n">
         <v>0.01027733225369439</v>
       </c>
+      <c r="AZ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1941,6 +2007,14 @@
       <c r="AY9" t="n">
         <v>0.01652937604135848</v>
       </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2098,6 +2172,14 @@
       <c r="AY10" t="n">
         <v>0.02727385976112988</v>
       </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2255,6 +2337,14 @@
       <c r="AY11" t="n">
         <v>0.008759089988944082</v>
       </c>
+      <c r="AZ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2412,6 +2502,14 @@
       <c r="AY12" t="n">
         <v>0.006781482115884707</v>
       </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2569,6 +2667,14 @@
       <c r="AY13" t="n">
         <v>0.03228795216368988</v>
       </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2726,6 +2832,14 @@
       <c r="AY14" t="n">
         <v>0.00872794655787228</v>
       </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2883,6 +2997,14 @@
       <c r="AY15" t="n">
         <v>0.007326492159641228</v>
       </c>
+      <c r="AZ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3040,6 +3162,14 @@
       <c r="AY16" t="n">
         <v>0.01536149737616593</v>
       </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>Middle East</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3197,6 +3327,14 @@
       <c r="AY17" t="n">
         <v>0.01846026876781015</v>
       </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Middle East</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3354,6 +3492,14 @@
       <c r="AY18" t="n">
         <v>0.007240847724193774</v>
       </c>
+      <c r="AZ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3511,6 +3657,14 @@
       <c r="AY19" t="n">
         <v>0.003347918840218627</v>
       </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>Oceania</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3668,6 +3822,14 @@
       <c r="AY20" t="n">
         <v>0.03786262632554228</v>
       </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3825,6 +3987,14 @@
       <c r="AY21" t="n">
         <v>0.0118890048116601</v>
       </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3982,6 +4152,14 @@
       <c r="AY22" t="n">
         <v>0.00899266572198259</v>
       </c>
+      <c r="AZ22" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4139,6 +4317,14 @@
       <c r="AY23" t="n">
         <v>0.01359410766284122</v>
       </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4296,6 +4482,14 @@
       <c r="AY24" t="n">
         <v>0.01346953393855401</v>
       </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4453,6 +4647,14 @@
       <c r="AY25" t="n">
         <v>0.01392889954686308</v>
       </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>Middle East</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4610,6 +4812,14 @@
       <c r="AY26" t="n">
         <v>0.01106370388825737</v>
       </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4767,6 +4977,14 @@
       <c r="AY27" t="n">
         <v>0.0171522446627945</v>
       </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4924,6 +5142,14 @@
       <c r="AY28" t="n">
         <v>0.004570298509786823</v>
       </c>
+      <c r="AZ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5081,6 +5307,14 @@
       <c r="AY29" t="n">
         <v>0.003877357168439247</v>
       </c>
+      <c r="AZ29" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -5238,6 +5472,14 @@
       <c r="AY30" t="n">
         <v>0.003503635995577633</v>
       </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5395,6 +5637,14 @@
       <c r="AY31" t="n">
         <v>0.01630358616608792</v>
       </c>
+      <c r="AZ31" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -5552,6 +5802,14 @@
       <c r="AY32" t="n">
         <v>0.004873946962736885</v>
       </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5709,6 +5967,14 @@
       <c r="AY33" t="n">
         <v>0.004671514660770177</v>
       </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5866,6 +6132,14 @@
       <c r="AY34" t="n">
         <v>0.004866161104968935</v>
       </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6023,6 +6297,14 @@
       <c r="AY35" t="n">
         <v>0.042137062240147</v>
       </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6180,6 +6462,14 @@
       <c r="AY36" t="n">
         <v>0.005076379264703592</v>
       </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6337,6 +6627,14 @@
       <c r="AY37" t="n">
         <v>0.00157274326912596</v>
       </c>
+      <c r="AZ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6494,6 +6792,14 @@
       <c r="AY38" t="n">
         <v>0.007739142621342593</v>
       </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6651,6 +6957,14 @@
       <c r="AY39" t="n">
         <v>0.001432597829302854</v>
       </c>
+      <c r="AZ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6808,6 +7122,14 @@
       <c r="AY40" t="n">
         <v>0.002670549214406951</v>
       </c>
+      <c r="AZ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6965,6 +7287,14 @@
       <c r="AY41" t="n">
         <v>0.003760569301919993</v>
       </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7122,6 +7452,14 @@
       <c r="AY42" t="n">
         <v>0.002530403774583846</v>
       </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7279,6 +7617,14 @@
       <c r="AY43" t="n">
         <v>0.002203397748329933</v>
       </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7436,6 +7782,14 @@
       <c r="AY44" t="n">
         <v>0.01155421292763824</v>
       </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7593,6 +7947,14 @@
       <c r="AY45" t="n">
         <v>0.002732836076550553</v>
       </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7750,6 +8112,14 @@
       <c r="AY46" t="n">
         <v>0.001642815989037512</v>
       </c>
+      <c r="AZ46" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA46" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7907,6 +8277,14 @@
       <c r="AY47" t="n">
         <v>0.005208738846758747</v>
       </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -8064,6 +8442,14 @@
       <c r="AY48" t="n">
         <v>0.006174185209984584</v>
       </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -8221,6 +8607,14 @@
       <c r="AY49" t="n">
         <v>0.004881732820504835</v>
       </c>
+      <c r="AZ49" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA49" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -8378,6 +8772,14 @@
       <c r="AY50" t="n">
         <v>0.004414581354427818</v>
       </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -8535,6 +8937,14 @@
       <c r="AY51" t="n">
         <v>0.003386848129058378</v>
       </c>
+      <c r="AZ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -8692,6 +9102,14 @@
       <c r="AY52" t="n">
         <v>0.003799498590759744</v>
       </c>
+      <c r="AZ52" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -8849,6 +9267,14 @@
       <c r="AY53" t="n">
         <v>0.00343356327566608</v>
       </c>
+      <c r="AZ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA53" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -9006,6 +9432,14 @@
       <c r="AY54" t="n">
         <v>0.001105591803048942</v>
       </c>
+      <c r="AZ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -9163,6 +9597,14 @@
       <c r="AY55" t="n">
         <v>0.008455441535994021</v>
       </c>
+      <c r="AZ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -9320,6 +9762,14 @@
       <c r="AY56" t="n">
         <v>0.002164468459490182</v>
       </c>
+      <c r="AZ56" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -9477,6 +9927,14 @@
       <c r="AY57" t="n">
         <v>0.004967377255952288</v>
       </c>
+      <c r="AZ57" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -9634,6 +10092,14 @@
       <c r="AY58" t="n">
         <v>0.00446908235880347</v>
       </c>
+      <c r="AZ58" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA58" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -9791,6 +10257,14 @@
       <c r="AY59" t="n">
         <v>0.004142076332549557</v>
       </c>
+      <c r="AZ59" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -9948,6 +10422,14 @@
       <c r="AY60" t="n">
         <v>0.009919182796368676</v>
       </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -10105,6 +10587,14 @@
       <c r="AY61" t="n">
         <v>0.005364456002117753</v>
       </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -10262,6 +10752,14 @@
       <c r="AY62" t="n">
         <v>0.0009109453588501845</v>
       </c>
+      <c r="AZ62" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -10419,6 +10917,14 @@
       <c r="AY63" t="n">
         <v>0.001487098833678506</v>
       </c>
+      <c r="AZ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -10576,6 +11082,14 @@
       <c r="AY64" t="n">
         <v>0.003052056245036516</v>
       </c>
+      <c r="AZ64" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -10733,6 +11247,14 @@
       <c r="AY65" t="n">
         <v>0.004663728803002227</v>
       </c>
+      <c r="AZ65" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -10890,6 +11412,14 @@
       <c r="AY66" t="n">
         <v>0.001448169544838755</v>
       </c>
+      <c r="AZ66" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -11047,6 +11577,14 @@
       <c r="AY67" t="n">
         <v>0.001300238247247699</v>
       </c>
+      <c r="AZ67" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -11204,6 +11742,14 @@
       <c r="AY68" t="n">
         <v>0.001269094816175898</v>
       </c>
+      <c r="AZ68" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -11361,6 +11907,14 @@
       <c r="AY69" t="n">
         <v>0.001097805945280992</v>
       </c>
+      <c r="AZ69" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -11518,6 +12072,14 @@
       <c r="AY70" t="n">
         <v>0.003106557249412168</v>
       </c>
+      <c r="AZ70" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -11675,6 +12237,14 @@
       <c r="AY71" t="n">
         <v>0.005387813575421604</v>
       </c>
+      <c r="AZ71" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -11832,6 +12402,14 @@
       <c r="AY72" t="n">
         <v>0.0006695837680437254</v>
       </c>
+      <c r="AZ72" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -11989,6 +12567,14 @@
       <c r="AY73" t="n">
         <v>0.003620423862096887</v>
       </c>
+      <c r="AZ73" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12146,6 +12732,14 @@
       <c r="AY74" t="n">
         <v>0.003075413818340367</v>
       </c>
+      <c r="AZ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -12303,6 +12897,14 @@
       <c r="AY75" t="n">
         <v>0.001105591803048942</v>
       </c>
+      <c r="AZ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -12460,6 +13062,14 @@
       <c r="AY76" t="n">
         <v>0.01369532381382457</v>
       </c>
+      <c r="AZ76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA76" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -12617,6 +13227,14 @@
       <c r="AY77" t="n">
         <v>0.001487098833678506</v>
       </c>
+      <c r="AZ77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12774,6 +13392,14 @@
       <c r="AY78" t="n">
         <v>0.005925037761410175</v>
       </c>
+      <c r="AZ78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12931,6 +13557,14 @@
       <c r="AY79" t="n">
         <v>0.0006540120525078247</v>
       </c>
+      <c r="AZ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA79" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13088,6 +13722,14 @@
       <c r="AY80" t="n">
         <v>0.004811660100593283</v>
       </c>
+      <c r="AZ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA80" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13245,6 +13887,14 @@
       <c r="AY81" t="n">
         <v>0.001440383687070804</v>
       </c>
+      <c r="AZ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA81" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -13402,6 +14052,14 @@
       <c r="AY82" t="n">
         <v>0.002693906787710802</v>
       </c>
+      <c r="AZ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA82" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13559,6 +14217,14 @@
       <c r="AY83" t="n">
         <v>0.002335757330385089</v>
       </c>
+      <c r="AZ83" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA83" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13716,6 +14382,14 @@
       <c r="AY84" t="n">
         <v>0.002857409800837759</v>
       </c>
+      <c r="AZ84" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA84" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13873,6 +14547,14 @@
       <c r="AY85" t="n">
         <v>0.001012161509833538</v>
       </c>
+      <c r="AZ85" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA85" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14030,6 +14712,14 @@
       <c r="AY86" t="n">
         <v>0.0009109453588501845</v>
       </c>
+      <c r="AZ86" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA86" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14187,6 +14877,14 @@
       <c r="AY87" t="n">
         <v>0.0004360080350052165</v>
       </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="inlineStr">
+        <is>
+          <t>Oceania</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14344,6 +15042,14 @@
       <c r="AY88" t="n">
         <v>0.0008642302122424827</v>
       </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14501,6 +15207,14 @@
       <c r="AY89" t="n">
         <v>0.0001790747286628568</v>
       </c>
+      <c r="AZ89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA89" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14658,6 +15372,14 @@
       <c r="AY90" t="n">
         <v>0.0006617979102757751</v>
       </c>
+      <c r="AZ90" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA90" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14815,6 +15537,14 @@
       <c r="AY91" t="n">
         <v>0.002351329045920989</v>
       </c>
+      <c r="AZ91" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14972,6 +15702,14 @@
       <c r="AY92" t="n">
         <v>0.001401454398231053</v>
       </c>
+      <c r="AZ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15129,6 +15867,14 @@
       <c r="AY93" t="n">
         <v>0.0008798019277783834</v>
       </c>
+      <c r="AZ93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA93" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15286,6 +16032,14 @@
       <c r="AY94" t="n">
         <v>0.0006695837680437254</v>
       </c>
+      <c r="AZ94" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15443,6 +16197,14 @@
       <c r="AY95" t="n">
         <v>0.00158052912689391</v>
       </c>
+      <c r="AZ95" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -15600,6 +16362,14 @@
       <c r="AY96" t="n">
         <v>0.005364456002117753</v>
       </c>
+      <c r="AZ96" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -15757,6 +16527,14 @@
       <c r="AY97" t="n">
         <v>0.0007396564879552781</v>
       </c>
+      <c r="AZ97" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -15914,6 +16692,14 @@
       <c r="AY98" t="n">
         <v>0.0002335757330385089</v>
       </c>
+      <c r="AZ98" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -16071,6 +16857,14 @@
       <c r="AY99" t="n">
         <v>0.003324561266914776</v>
       </c>
+      <c r="AZ99" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -16228,6 +17022,14 @@
       <c r="AY100" t="n">
         <v>0.0001946464441987574</v>
       </c>
+      <c r="AZ100" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -16385,6 +17187,14 @@
       <c r="AY101" t="n">
         <v>0.000685155483579626</v>
       </c>
+      <c r="AZ101" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -16542,6 +17352,14 @@
       <c r="AY102" t="n">
         <v>0.001160092807424594</v>
       </c>
+      <c r="AZ102" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -16699,6 +17517,14 @@
       <c r="AY103" t="n">
         <v>0.000210218159734658</v>
       </c>
+      <c r="AZ103" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -16856,6 +17682,14 @@
       <c r="AY104" t="n">
         <v>0.0005138666126847194</v>
       </c>
+      <c r="AZ104" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -17013,6 +17847,14 @@
       <c r="AY105" t="n">
         <v>0.0004126504617013656</v>
       </c>
+      <c r="AZ105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -17170,6 +18012,14 @@
       <c r="AY106" t="n">
         <v>0.001728460424484965</v>
       </c>
+      <c r="AZ106" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -17327,6 +18177,14 @@
       <c r="AY107" t="n">
         <v>0.001782961428860618</v>
       </c>
+      <c r="AZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -17484,6 +18342,14 @@
       <c r="AY108" t="n">
         <v>0.0001012161509833538</v>
       </c>
+      <c r="AZ108" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA108" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -17641,6 +18507,14 @@
       <c r="AY109" t="n">
         <v>0.0004905090393808686</v>
       </c>
+      <c r="AZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -17798,6 +18672,14 @@
       <c r="AY110" t="n">
         <v>0.0008720160700104331</v>
       </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -17955,6 +18837,14 @@
       <c r="AY111" t="n">
         <v>0.0003659353150936638</v>
       </c>
+      <c r="AZ111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -18112,6 +19002,14 @@
       <c r="AY112" t="n">
         <v>0.0008564443544745325</v>
       </c>
+      <c r="AZ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -18269,6 +19167,14 @@
       <c r="AY113" t="n">
         <v>0.0003114343107180118</v>
       </c>
+      <c r="AZ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -18426,6 +19332,14 @@
       <c r="AY114" t="n">
         <v>0.0003892928883975147</v>
       </c>
+      <c r="AZ114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -18583,6 +19497,14 @@
       <c r="AY115" t="n">
         <v>0.002413615908064591</v>
       </c>
+      <c r="AZ115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -18740,6 +19662,14 @@
       <c r="AY116" t="n">
         <v>0.002024323019667077</v>
       </c>
+      <c r="AZ116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -18897,6 +19827,14 @@
       <c r="AY117" t="n">
         <v>0.0004126504617013656</v>
       </c>
+      <c r="AZ117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -19054,6 +19992,14 @@
       <c r="AY118" t="n">
         <v>7.785857767950296e-06</v>
       </c>
+      <c r="AZ118" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -19213,6 +20159,14 @@
       <c r="AY119" t="n">
         <v>7.007271991155266e-05</v>
       </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -19370,6 +20324,14 @@
       <c r="AY120" t="n">
         <v>0.0002024323019667077</v>
       </c>
+      <c r="AZ120" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -19527,6 +20489,14 @@
       <c r="AY121" t="n">
         <v>0.0008408726389386318</v>
       </c>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -19684,6 +20654,14 @@
       <c r="AY122" t="n">
         <v>0.0003659353150936638</v>
       </c>
+      <c r="AZ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -19841,6 +20819,14 @@
       <c r="AY123" t="n">
         <v>0.0007007271991155265</v>
       </c>
+      <c r="AZ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -19998,6 +20984,14 @@
       <c r="AY124" t="n">
         <v>0.0004282221772372662</v>
       </c>
+      <c r="AZ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20155,6 +21149,14 @@
       <c r="AY125" t="n">
         <v>0.0009187312166181348</v>
       </c>
+      <c r="AZ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20312,6 +21314,14 @@
       <c r="AY126" t="n">
         <v>0.000342577741789813</v>
       </c>
+      <c r="AZ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20469,6 +21479,14 @@
       <c r="AY127" t="n">
         <v>0.0001167878665192544</v>
       </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -20626,6 +21644,14 @@
       <c r="AY128" t="n">
         <v>0.0001946464441987574</v>
       </c>
+      <c r="AZ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -20783,6 +21809,14 @@
       <c r="AY129" t="n">
         <v>0.0005138666126847194</v>
       </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -20940,6 +21974,14 @@
       <c r="AY130" t="n">
         <v>0.0001946464441987574</v>
       </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -21097,6 +22139,14 @@
       <c r="AY131" t="n">
         <v>0.000132359582055155</v>
       </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21254,6 +22304,14 @@
       <c r="AY132" t="n">
         <v>0.001004375652065588</v>
       </c>
+      <c r="AZ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21411,6 +22469,14 @@
       <c r="AY133" t="n">
         <v>0.0005216524704526698</v>
       </c>
+      <c r="AZ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21568,6 +22634,14 @@
       <c r="AY134" t="n">
         <v>0.0002257898752705586</v>
       </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21724,6 +22798,14 @@
       </c>
       <c r="AY135" t="n">
         <v>2.335757330385089e-05</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -21878,6 +22960,14 @@
       <c r="AY136" t="n">
         <v>0</v>
       </c>
+      <c r="AZ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -22037,6 +23127,14 @@
       <c r="AY137" t="n">
         <v>0.0005294383282206201</v>
       </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22194,6 +23292,14 @@
       <c r="AY138" t="n">
         <v>8.564443544745325e-05</v>
       </c>
+      <c r="AZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22351,6 +23457,14 @@
       <c r="AY139" t="n">
         <v>3.114343107180118e-05</v>
       </c>
+      <c r="AZ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -22508,6 +23622,14 @@
       <c r="AY140" t="n">
         <v>0.0001557171553590059</v>
       </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22664,6 +23786,14 @@
       </c>
       <c r="AY141" t="n">
         <v>6.228686214360237e-05</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -22816,6 +23946,14 @@
       <c r="AY142" t="n">
         <v>0</v>
       </c>
+      <c r="AZ142" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -22973,6 +24111,14 @@
       <c r="AY143" t="n">
         <v>7.785857767950295e-05</v>
       </c>
+      <c r="AZ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -23130,6 +24276,14 @@
       <c r="AY144" t="n">
         <v>4.671514660770177e-05</v>
       </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -23287,6 +24441,14 @@
       <c r="AY145" t="n">
         <v>5.450100437565207e-05</v>
       </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -23443,6 +24605,14 @@
       </c>
       <c r="AY146" t="n">
         <v>1.557171553590059e-05</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
       </c>
     </row>
   </sheetData>
